--- a/Config/Datas/human_civilization_attribute.xlsx
+++ b/Config/Datas/human_civilization_attribute.xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
@@ -1232,7 +1232,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
@@ -1248,7 +1248,7 @@
           <t>TownManagementAccess</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="n">
         <v>1</v>
       </c>
@@ -1264,7 +1264,7 @@
           <t>ScavengeExchangeAccess</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="n">
         <v>2</v>
       </c>
@@ -1280,7 +1280,7 @@
           <t>TavernHumanKnowledgeOutput</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
@@ -1296,7 +1296,7 @@
           <t>BasicWoodworkingAccess</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
@@ -1312,7 +1312,7 @@
           <t>TownStabilityBonus</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="n">
         <v>5</v>
       </c>
@@ -1328,7 +1328,7 @@
           <t>WorkshopOperationEfficiency</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="n">
         <v>6</v>
       </c>
@@ -1346,7 +1346,7 @@
           <t>TownInfluenceGainBonus</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="n">
         <v>7</v>
       </c>
@@ -1362,7 +1362,7 @@
           <t>ExplorationLootValueBonus</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
@@ -1378,7 +1378,7 @@
           <t>HumanKnowledgeGainBonus</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
@@ -1388,6 +1388,27 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>TownFacilityGoldOutput</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Town facility gold output bonus tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Datas/human_civilization_attribute.xlsx
+++ b/Config/Datas/human_civilization_attribute.xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
@@ -1403,12 +1403,21 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MarketSalePriceBonus</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Market sale price bonus percent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
